--- a/output/pdf_financials_xlsx/GSPR.xlsx
+++ b/output/pdf_financials_xlsx/GSPR.xlsx
@@ -901,10 +901,10 @@
         <v>0.285568</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.5579499999999999</v>
+        <v>-0.5579499999999999</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.55126</v>
+        <v>-0.55126</v>
       </c>
     </row>
     <row r="17">
@@ -914,22 +914,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.025377</v>
+        <v>-0.031167</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0.02574</v>
+        <v>-0.476914</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0.02426</v>
+        <v>-0.5634439999999999</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.035</v>
+        <v>-1.02366</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0.015819</v>
+        <v>-0.692271</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.003378</v>
+        <v>-0.574514</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>-0</v>
@@ -1039,28 +1039,28 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.028272</v>
+        <v>-0.028272</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.225587</v>
+        <v>-0.225587</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.269592</v>
+        <v>-0.269592</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.49433</v>
+        <v>-0.49433</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.338226</v>
+        <v>-0.338226</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.288946</v>
+        <v>-0.288946</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.5579499999999999</v>
+        <v>-0.5579499999999999</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.55126</v>
+        <v>-0.55126</v>
       </c>
     </row>
     <row r="21">
@@ -1132,28 +1132,28 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.028272</v>
+        <v>-0.028272</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.225587</v>
+        <v>-0.225587</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.269592</v>
+        <v>-0.269592</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.49433</v>
+        <v>-0.49433</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.338226</v>
+        <v>-0.338226</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.288946</v>
+        <v>-0.288946</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.5579499999999999</v>
+        <v>-0.5579499999999999</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.55126</v>
+        <v>-0.55126</v>
       </c>
     </row>
     <row r="24">
@@ -1230,16 +1230,16 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-7.519567</v>
+        <v>7.519567</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-13.4796</v>
+        <v>13.4796</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-16.477667</v>
+        <v>16.477667</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-16.9113</v>
+        <v>16.9113</v>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-27.8975</v>
+        <v>27.8975</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
@@ -1280,10 +1280,10 @@
         <v>0.285568</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.5579499999999999</v>
+        <v>-0.5579499999999999</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.55126</v>
+        <v>-0.55126</v>
       </c>
     </row>
     <row r="28">
@@ -1342,10 +1342,10 @@
         <v>0.285568</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.5579499999999999</v>
+        <v>-0.5579499999999999</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.55126</v>
+        <v>-0.55126</v>
       </c>
     </row>
     <row r="30">
@@ -1402,28 +1402,28 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>876.5803108808291</v>
+        <v>1076.580310880829</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>10.24163738874057</v>
+        <v>189.7583626112595</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>8.255856689762194</v>
+        <v>191.7441433102378</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>6.612132318213591</v>
+        <v>193.3878676817864</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>4.4680760920222</v>
+        <v>195.5319239079778</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>1.182905647691618</v>
+        <v>201.1829056476916</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -3344,25 +3344,25 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.196119</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.242511</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.410232</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.5292559999999999</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.564469</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.785426</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.916745</v>
       </c>
     </row>
     <row r="93">
@@ -5366,7 +5366,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -6338,7 +6342,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -9589,25 +9597,25 @@
         </is>
       </c>
       <c r="F95" s="5" t="n">
-        <v>0.225587</v>
+        <v>-0.225587</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.269592</v>
+        <v>-0.269592</v>
       </c>
       <c r="H95" s="5" t="n">
-        <v>0.49433</v>
+        <v>-0.49433</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>0.338226</v>
+        <v>-0.338226</v>
       </c>
       <c r="J95" s="5" t="n">
-        <v>0.288946</v>
+        <v>-0.288946</v>
       </c>
       <c r="K95" s="5" t="n">
-        <v>0.5579499999999999</v>
+        <v>-0.5579499999999999</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>0.55126</v>
+        <v>-0.55126</v>
       </c>
     </row>
     <row r="96">
@@ -10922,10 +10930,10 @@
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>0.028272</v>
+        <v>-0.028272</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>0.225587</v>
+        <v>-0.225587</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/GSPR.xlsx
+++ b/output/pdf_financials_xlsx/GSPR.xlsx
@@ -771,16 +771,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000899</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>9.3e-05</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.001106</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.001227</v>
       </c>
     </row>
     <row r="13">
@@ -1274,16 +1274,16 @@
         <v>0.52933</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.354045</v>
+        <v>0.353146</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.285568</v>
+        <v>0.285475</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.5579499999999999</v>
+        <v>-0.559056</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.55126</v>
+        <v>-0.552487</v>
       </c>
     </row>
     <row r="28">
@@ -1336,16 +1336,16 @@
         <v>0.52933</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.354045</v>
+        <v>0.353146</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.285568</v>
+        <v>0.285475</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.5579499999999999</v>
+        <v>-0.559056</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.55126</v>
+        <v>-0.552487</v>
       </c>
     </row>
     <row r="30">
@@ -1487,28 +1487,28 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.244452</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.5236189999999999</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.524187</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.70838</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.240116</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.189063</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.135408</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.428023</v>
       </c>
     </row>
     <row r="35">
@@ -1549,28 +1549,28 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.244452</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.5236189999999999</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.524187</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.043</v>
+        <v>0.75138</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.007</v>
+        <v>0.247116</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.0056</v>
+        <v>0.194663</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.0045</v>
+        <v>0.139908</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.003</v>
+        <v>0.431023</v>
       </c>
     </row>
     <row r="37">
@@ -1921,28 +1921,28 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.244452</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.5296380000000001</v>
+        <v>0.006019</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.602823</v>
+        <v>0.078636</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.7694569999999999</v>
+        <v>0.061077</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.249641</v>
+        <v>0.009525</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.19896</v>
+        <v>0.009897</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.162275</v>
+        <v>0.026867</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.502444</v>
+        <v>0.074421</v>
       </c>
     </row>
     <row r="49">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">

--- a/output/pdf_financials_xlsx/GSPR.xlsx
+++ b/output/pdf_financials_xlsx/GSPR.xlsx
@@ -3596,22 +3596,22 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.005571</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.016704</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.015875</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.00121</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>0.001364</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000348</v>
       </c>
       <c r="H101" s="3" t="n">
         <v>0</v>
@@ -3751,22 +3751,22 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.005925</v>
+        <v>0.000354</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.011944</v>
+        <v>-0.028648</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.059547</v>
+        <v>-0.043672</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.011834</v>
+        <v>0.010624</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.045341</v>
+        <v>0.046705</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.051644</v>
+        <v>0.051296</v>
       </c>
       <c r="H106" s="3" t="n">
         <v>-0.029186</v>
@@ -7936,7 +7936,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -7988,7 +7992,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E64" s="5" t="n">
         <v>-0.005571</v>
       </c>
@@ -8522,7 +8530,11 @@
           <t>Deferred tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E74" s="5" t="n">
         <v>0.025377</v>
       </c>
